--- a/data/Truth.xlsx
+++ b/data/Truth.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Dropbox\AI Projects\otter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\AI Projects\otter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F09D794-6EC6-4B12-985B-9408AE6014D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF0F2F9-8BFF-48A6-9257-612E5E2A238A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6915" yWindow="2685" windowWidth="18795" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33435" yWindow="0" windowWidth="18525" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="202">
   <si>
     <t>Image</t>
   </si>
@@ -567,6 +567,84 @@
   </si>
   <si>
     <t>250816_BSHNL_0</t>
+  </si>
+  <si>
+    <t>260125_TC1_0</t>
+  </si>
+  <si>
+    <t>260120_STLTH_0</t>
+  </si>
+  <si>
+    <t>260121_BSHNL_0</t>
+  </si>
+  <si>
+    <t>260122_KEN1_0</t>
+  </si>
+  <si>
+    <t>260122_KEN1_1</t>
+  </si>
+  <si>
+    <t>260122_TC1_0</t>
+  </si>
+  <si>
+    <t>260124_TC1_0</t>
+  </si>
+  <si>
+    <t>260126_BSHNL_0</t>
+  </si>
+  <si>
+    <t>260131_KEN1_0</t>
+  </si>
+  <si>
+    <t>260201_TC1_1</t>
+  </si>
+  <si>
+    <t>260201_TC1_2</t>
+  </si>
+  <si>
+    <t>260114_BSHNL_0</t>
+  </si>
+  <si>
+    <t>260113_TC1_0</t>
+  </si>
+  <si>
+    <t>260115_TC1_0</t>
+  </si>
+  <si>
+    <t>260117_TC1_0</t>
+  </si>
+  <si>
+    <t>260115_TC1_1</t>
+  </si>
+  <si>
+    <t>060313_BSHNL_0</t>
+  </si>
+  <si>
+    <t>260207_STLTH_0</t>
+  </si>
+  <si>
+    <t>260209_TC1_0</t>
+  </si>
+  <si>
+    <t>260208_TC1_0</t>
+  </si>
+  <si>
+    <t>260208_BSHNL_0</t>
+  </si>
+  <si>
+    <t>260207_BSHNL_0</t>
+  </si>
+  <si>
+    <t>260207_KEN1_0</t>
+  </si>
+  <si>
+    <t>260207_STLTH_1</t>
+  </si>
+  <si>
+    <t>260207_STLTH_2</t>
+  </si>
+  <si>
+    <t>260206_KEN1_0</t>
   </si>
 </sst>
 </file>
@@ -911,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R159"/>
+  <dimension ref="A1:R186"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="1" customWidth="1"/>
@@ -8014,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="1">
-        <f t="shared" ref="G130:G159" si="6">SUM(E130:F130)</f>
+        <f t="shared" ref="G130:G171" si="6">SUM(E130:F130)</f>
         <v>2</v>
       </c>
       <c r="H130" s="1">
@@ -9701,6 +9779,1545 @@
         <v>0</v>
       </c>
       <c r="R159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B160" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C160" s="1">
+        <v>1</v>
+      </c>
+      <c r="D160" s="1">
+        <v>14</v>
+      </c>
+      <c r="E160" s="1">
+        <v>0</v>
+      </c>
+      <c r="F160" s="1">
+        <v>0</v>
+      </c>
+      <c r="G160" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H160" s="1">
+        <v>0</v>
+      </c>
+      <c r="I160" s="1">
+        <v>0</v>
+      </c>
+      <c r="J160" s="1">
+        <v>9</v>
+      </c>
+      <c r="K160" s="1">
+        <v>0</v>
+      </c>
+      <c r="L160" s="1">
+        <v>0</v>
+      </c>
+      <c r="M160" s="1">
+        <v>0</v>
+      </c>
+      <c r="N160" s="1">
+        <v>0</v>
+      </c>
+      <c r="O160" s="1">
+        <v>0</v>
+      </c>
+      <c r="P160" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="1">
+        <v>0</v>
+      </c>
+      <c r="R160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B161" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C161" s="1">
+        <v>1</v>
+      </c>
+      <c r="D161" s="1">
+        <v>13</v>
+      </c>
+      <c r="E161" s="1">
+        <v>1</v>
+      </c>
+      <c r="F161" s="1">
+        <v>0</v>
+      </c>
+      <c r="G161" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="H161" s="1">
+        <v>0</v>
+      </c>
+      <c r="I161" s="1">
+        <v>0</v>
+      </c>
+      <c r="J161" s="1">
+        <v>0</v>
+      </c>
+      <c r="K161" s="1">
+        <v>0</v>
+      </c>
+      <c r="L161" s="1">
+        <v>0</v>
+      </c>
+      <c r="M161" s="1">
+        <v>0</v>
+      </c>
+      <c r="N161" s="1">
+        <v>0</v>
+      </c>
+      <c r="O161" s="1">
+        <v>0</v>
+      </c>
+      <c r="P161" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="1">
+        <v>0</v>
+      </c>
+      <c r="R161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B162" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C162" s="1">
+        <v>1</v>
+      </c>
+      <c r="D162" s="1">
+        <v>15</v>
+      </c>
+      <c r="E162" s="1">
+        <v>1</v>
+      </c>
+      <c r="F162" s="1">
+        <v>0</v>
+      </c>
+      <c r="G162" s="1">
+        <f t="shared" ref="G162:G165" si="7">SUM(E162:F162)</f>
+        <v>1</v>
+      </c>
+      <c r="H162" s="1">
+        <v>0</v>
+      </c>
+      <c r="I162" s="1">
+        <v>0</v>
+      </c>
+      <c r="J162" s="1">
+        <v>0</v>
+      </c>
+      <c r="K162" s="1">
+        <v>0</v>
+      </c>
+      <c r="L162" s="1">
+        <v>0</v>
+      </c>
+      <c r="M162" s="1">
+        <v>0</v>
+      </c>
+      <c r="N162" s="1">
+        <v>0</v>
+      </c>
+      <c r="O162" s="1">
+        <v>0</v>
+      </c>
+      <c r="P162" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q162" s="1">
+        <v>0</v>
+      </c>
+      <c r="R162" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B163" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C163" s="1">
+        <v>1</v>
+      </c>
+      <c r="D163" s="1">
+        <v>15</v>
+      </c>
+      <c r="E163" s="1">
+        <v>1</v>
+      </c>
+      <c r="F163" s="1">
+        <v>0</v>
+      </c>
+      <c r="G163" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H163" s="1">
+        <v>0</v>
+      </c>
+      <c r="I163" s="1">
+        <v>0</v>
+      </c>
+      <c r="J163" s="1">
+        <v>0</v>
+      </c>
+      <c r="K163" s="1">
+        <v>0</v>
+      </c>
+      <c r="L163" s="1">
+        <v>0</v>
+      </c>
+      <c r="M163" s="1">
+        <v>0</v>
+      </c>
+      <c r="N163" s="1">
+        <v>0</v>
+      </c>
+      <c r="O163" s="1">
+        <v>0</v>
+      </c>
+      <c r="P163" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q163" s="1">
+        <v>0</v>
+      </c>
+      <c r="R163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B164" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C164" s="1">
+        <v>1</v>
+      </c>
+      <c r="D164" s="1">
+        <v>17</v>
+      </c>
+      <c r="E164" s="1">
+        <v>1</v>
+      </c>
+      <c r="F164" s="1">
+        <v>0</v>
+      </c>
+      <c r="G164" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H164" s="1">
+        <v>0</v>
+      </c>
+      <c r="I164" s="1">
+        <v>0</v>
+      </c>
+      <c r="J164" s="1">
+        <v>0</v>
+      </c>
+      <c r="K164" s="1">
+        <v>0</v>
+      </c>
+      <c r="L164" s="1">
+        <v>0</v>
+      </c>
+      <c r="M164" s="1">
+        <v>0</v>
+      </c>
+      <c r="N164" s="1">
+        <v>0</v>
+      </c>
+      <c r="O164" s="1">
+        <v>0</v>
+      </c>
+      <c r="P164" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q164" s="1">
+        <v>0</v>
+      </c>
+      <c r="R164" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B165" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C165" s="1">
+        <v>1</v>
+      </c>
+      <c r="D165" s="1">
+        <v>20</v>
+      </c>
+      <c r="E165" s="1">
+        <v>1</v>
+      </c>
+      <c r="F165" s="1">
+        <v>0</v>
+      </c>
+      <c r="G165" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H165" s="1">
+        <v>0</v>
+      </c>
+      <c r="I165" s="1">
+        <v>0</v>
+      </c>
+      <c r="J165" s="1">
+        <v>0</v>
+      </c>
+      <c r="K165" s="1">
+        <v>0</v>
+      </c>
+      <c r="L165" s="1">
+        <v>0</v>
+      </c>
+      <c r="M165" s="1">
+        <v>0</v>
+      </c>
+      <c r="N165" s="1">
+        <v>0</v>
+      </c>
+      <c r="O165" s="1">
+        <v>0</v>
+      </c>
+      <c r="P165" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q165" s="1">
+        <v>0</v>
+      </c>
+      <c r="R165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B166" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C166" s="1">
+        <v>1</v>
+      </c>
+      <c r="D166" s="1">
+        <v>20</v>
+      </c>
+      <c r="E166" s="1">
+        <v>1</v>
+      </c>
+      <c r="F166" s="1">
+        <v>0</v>
+      </c>
+      <c r="G166" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="H166" s="1">
+        <v>0</v>
+      </c>
+      <c r="I166" s="1">
+        <v>0</v>
+      </c>
+      <c r="J166" s="1">
+        <v>0</v>
+      </c>
+      <c r="K166" s="1">
+        <v>0</v>
+      </c>
+      <c r="L166" s="1">
+        <v>0</v>
+      </c>
+      <c r="M166" s="1">
+        <v>0</v>
+      </c>
+      <c r="N166" s="1">
+        <v>0</v>
+      </c>
+      <c r="O166" s="1">
+        <v>0</v>
+      </c>
+      <c r="P166" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="1">
+        <v>0</v>
+      </c>
+      <c r="R166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B167" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C167" s="1">
+        <v>1</v>
+      </c>
+      <c r="D167" s="1">
+        <v>21</v>
+      </c>
+      <c r="E167" s="1">
+        <v>2</v>
+      </c>
+      <c r="F167" s="1">
+        <v>0</v>
+      </c>
+      <c r="G167" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H167" s="1">
+        <v>0</v>
+      </c>
+      <c r="I167" s="1">
+        <v>0</v>
+      </c>
+      <c r="J167" s="1">
+        <v>0</v>
+      </c>
+      <c r="K167" s="1">
+        <v>0</v>
+      </c>
+      <c r="L167" s="1">
+        <v>0</v>
+      </c>
+      <c r="M167" s="1">
+        <v>0</v>
+      </c>
+      <c r="N167" s="1">
+        <v>0</v>
+      </c>
+      <c r="O167" s="1">
+        <v>0</v>
+      </c>
+      <c r="P167" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="1">
+        <v>0</v>
+      </c>
+      <c r="R167" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B168" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C168" s="1">
+        <v>1</v>
+      </c>
+      <c r="D168" s="1">
+        <v>22</v>
+      </c>
+      <c r="E168" s="1">
+        <v>0</v>
+      </c>
+      <c r="F168" s="1">
+        <v>0</v>
+      </c>
+      <c r="G168" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H168" s="1">
+        <v>0</v>
+      </c>
+      <c r="I168" s="1">
+        <v>0</v>
+      </c>
+      <c r="J168" s="1">
+        <v>0</v>
+      </c>
+      <c r="K168" s="1">
+        <v>0</v>
+      </c>
+      <c r="L168" s="1">
+        <v>1</v>
+      </c>
+      <c r="M168" s="1">
+        <v>0</v>
+      </c>
+      <c r="N168" s="1">
+        <v>0</v>
+      </c>
+      <c r="O168" s="1">
+        <v>0</v>
+      </c>
+      <c r="P168" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="1">
+        <v>0</v>
+      </c>
+      <c r="R168" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B169" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C169" s="1">
+        <v>1</v>
+      </c>
+      <c r="D169" s="1">
+        <v>22</v>
+      </c>
+      <c r="E169" s="1">
+        <v>1</v>
+      </c>
+      <c r="F169" s="1">
+        <v>0</v>
+      </c>
+      <c r="G169" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="H169" s="1">
+        <v>0</v>
+      </c>
+      <c r="I169" s="1">
+        <v>0</v>
+      </c>
+      <c r="J169" s="1">
+        <v>0</v>
+      </c>
+      <c r="K169" s="1">
+        <v>0</v>
+      </c>
+      <c r="L169" s="1">
+        <v>0</v>
+      </c>
+      <c r="M169" s="1">
+        <v>0</v>
+      </c>
+      <c r="N169" s="1">
+        <v>0</v>
+      </c>
+      <c r="O169" s="1">
+        <v>0</v>
+      </c>
+      <c r="P169" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="1">
+        <v>0</v>
+      </c>
+      <c r="R169" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B170" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C170" s="1">
+        <v>1</v>
+      </c>
+      <c r="D170" s="1">
+        <v>22</v>
+      </c>
+      <c r="E170" s="1">
+        <v>0</v>
+      </c>
+      <c r="F170" s="1">
+        <v>0</v>
+      </c>
+      <c r="G170" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H170" s="1">
+        <v>2</v>
+      </c>
+      <c r="I170" s="1">
+        <v>0</v>
+      </c>
+      <c r="J170" s="1">
+        <v>0</v>
+      </c>
+      <c r="K170" s="1">
+        <v>0</v>
+      </c>
+      <c r="L170" s="1">
+        <v>0</v>
+      </c>
+      <c r="M170" s="1">
+        <v>0</v>
+      </c>
+      <c r="N170" s="1">
+        <v>0</v>
+      </c>
+      <c r="O170" s="1">
+        <v>0</v>
+      </c>
+      <c r="P170" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="1">
+        <v>0</v>
+      </c>
+      <c r="R170" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B171" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C171" s="1">
+        <v>1</v>
+      </c>
+      <c r="D171" s="1">
+        <v>24</v>
+      </c>
+      <c r="E171" s="1">
+        <v>0</v>
+      </c>
+      <c r="F171" s="1">
+        <v>0</v>
+      </c>
+      <c r="G171" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H171" s="1">
+        <v>1</v>
+      </c>
+      <c r="I171" s="1">
+        <v>0</v>
+      </c>
+      <c r="J171" s="1">
+        <v>0</v>
+      </c>
+      <c r="K171" s="1">
+        <v>0</v>
+      </c>
+      <c r="L171" s="1">
+        <v>0</v>
+      </c>
+      <c r="M171" s="1">
+        <v>0</v>
+      </c>
+      <c r="N171" s="1">
+        <v>0</v>
+      </c>
+      <c r="O171" s="1">
+        <v>0</v>
+      </c>
+      <c r="P171" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="1">
+        <v>0</v>
+      </c>
+      <c r="R171" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B172" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C172" s="1">
+        <v>1</v>
+      </c>
+      <c r="D172" s="1">
+        <v>25</v>
+      </c>
+      <c r="E172" s="1">
+        <v>0</v>
+      </c>
+      <c r="F172" s="1">
+        <v>0</v>
+      </c>
+      <c r="G172" s="1">
+        <f t="shared" ref="G172:G188" si="8">SUM(E172:F172)</f>
+        <v>0</v>
+      </c>
+      <c r="H172" s="1">
+        <v>1</v>
+      </c>
+      <c r="I172" s="1">
+        <v>0</v>
+      </c>
+      <c r="J172" s="1">
+        <v>0</v>
+      </c>
+      <c r="K172" s="1">
+        <v>0</v>
+      </c>
+      <c r="L172" s="1">
+        <v>0</v>
+      </c>
+      <c r="M172" s="1">
+        <v>0</v>
+      </c>
+      <c r="N172" s="1">
+        <v>0</v>
+      </c>
+      <c r="O172" s="1">
+        <v>0</v>
+      </c>
+      <c r="P172" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="1">
+        <v>0</v>
+      </c>
+      <c r="R172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B173" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C173" s="1">
+        <v>1</v>
+      </c>
+      <c r="D173" s="1">
+        <v>26</v>
+      </c>
+      <c r="E173" s="1">
+        <v>0</v>
+      </c>
+      <c r="F173" s="1">
+        <v>0</v>
+      </c>
+      <c r="G173" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H173" s="1">
+        <v>0</v>
+      </c>
+      <c r="I173" s="1">
+        <v>0</v>
+      </c>
+      <c r="J173" s="1">
+        <v>6</v>
+      </c>
+      <c r="K173" s="1">
+        <v>0</v>
+      </c>
+      <c r="L173" s="1">
+        <v>0</v>
+      </c>
+      <c r="M173" s="1">
+        <v>0</v>
+      </c>
+      <c r="N173" s="1">
+        <v>0</v>
+      </c>
+      <c r="O173" s="1">
+        <v>0</v>
+      </c>
+      <c r="P173" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="1">
+        <v>0</v>
+      </c>
+      <c r="R173" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B174" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C174" s="1">
+        <v>1</v>
+      </c>
+      <c r="D174" s="1">
+        <v>31</v>
+      </c>
+      <c r="E174" s="1">
+        <v>1</v>
+      </c>
+      <c r="F174" s="1">
+        <v>0</v>
+      </c>
+      <c r="G174" s="1">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H174" s="1">
+        <v>0</v>
+      </c>
+      <c r="I174" s="1">
+        <v>0</v>
+      </c>
+      <c r="J174" s="1">
+        <v>6</v>
+      </c>
+      <c r="K174" s="1">
+        <v>0</v>
+      </c>
+      <c r="L174" s="1">
+        <v>0</v>
+      </c>
+      <c r="M174" s="1">
+        <v>0</v>
+      </c>
+      <c r="N174" s="1">
+        <v>0</v>
+      </c>
+      <c r="O174" s="1">
+        <v>0</v>
+      </c>
+      <c r="P174" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="1">
+        <v>0</v>
+      </c>
+      <c r="R174" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B175" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C175" s="1">
+        <v>2</v>
+      </c>
+      <c r="D175" s="1">
+        <v>1</v>
+      </c>
+      <c r="E175" s="1">
+        <v>2</v>
+      </c>
+      <c r="F175" s="1">
+        <v>1</v>
+      </c>
+      <c r="G175" s="1">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="H175" s="1">
+        <v>0</v>
+      </c>
+      <c r="I175" s="1">
+        <v>0</v>
+      </c>
+      <c r="J175" s="1">
+        <v>6</v>
+      </c>
+      <c r="K175" s="1">
+        <v>0</v>
+      </c>
+      <c r="L175" s="1">
+        <v>0</v>
+      </c>
+      <c r="M175" s="1">
+        <v>0</v>
+      </c>
+      <c r="N175" s="1">
+        <v>0</v>
+      </c>
+      <c r="O175" s="1">
+        <v>0</v>
+      </c>
+      <c r="P175" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="1">
+        <v>0</v>
+      </c>
+      <c r="R175" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B176" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C176" s="1">
+        <v>2</v>
+      </c>
+      <c r="D176" s="1">
+        <v>1</v>
+      </c>
+      <c r="E176" s="1">
+        <v>3</v>
+      </c>
+      <c r="F176" s="1">
+        <v>1</v>
+      </c>
+      <c r="G176" s="1">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="H176" s="1">
+        <v>0</v>
+      </c>
+      <c r="I176" s="1">
+        <v>0</v>
+      </c>
+      <c r="J176" s="1">
+        <v>6</v>
+      </c>
+      <c r="K176" s="1">
+        <v>0</v>
+      </c>
+      <c r="L176" s="1">
+        <v>0</v>
+      </c>
+      <c r="M176" s="1">
+        <v>0</v>
+      </c>
+      <c r="N176" s="1">
+        <v>0</v>
+      </c>
+      <c r="O176" s="1">
+        <v>0</v>
+      </c>
+      <c r="P176" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="1">
+        <v>0</v>
+      </c>
+      <c r="R176" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B177" s="1">
+        <v>2006</v>
+      </c>
+      <c r="C177" s="1">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1">
+        <v>13</v>
+      </c>
+      <c r="E177" s="1">
+        <v>0</v>
+      </c>
+      <c r="F177" s="1">
+        <v>0</v>
+      </c>
+      <c r="G177" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H177" s="1">
+        <v>0</v>
+      </c>
+      <c r="I177" s="1">
+        <v>0</v>
+      </c>
+      <c r="J177" s="1">
+        <v>76</v>
+      </c>
+      <c r="K177" s="1">
+        <v>0</v>
+      </c>
+      <c r="L177" s="1">
+        <v>0</v>
+      </c>
+      <c r="M177" s="1">
+        <v>0</v>
+      </c>
+      <c r="N177" s="1">
+        <v>0</v>
+      </c>
+      <c r="O177" s="1">
+        <v>0</v>
+      </c>
+      <c r="P177" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="1">
+        <v>0</v>
+      </c>
+      <c r="R177" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B178" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C178" s="1">
+        <v>2</v>
+      </c>
+      <c r="D178" s="1">
+        <v>7</v>
+      </c>
+      <c r="E178" s="1">
+        <v>0</v>
+      </c>
+      <c r="F178" s="1">
+        <v>0</v>
+      </c>
+      <c r="G178" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H178" s="1">
+        <v>0</v>
+      </c>
+      <c r="I178" s="1">
+        <v>0</v>
+      </c>
+      <c r="J178" s="1">
+        <v>7</v>
+      </c>
+      <c r="K178" s="1">
+        <v>0</v>
+      </c>
+      <c r="L178" s="1">
+        <v>0</v>
+      </c>
+      <c r="M178" s="1">
+        <v>0</v>
+      </c>
+      <c r="N178" s="1">
+        <v>0</v>
+      </c>
+      <c r="O178" s="1">
+        <v>0</v>
+      </c>
+      <c r="P178" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="1">
+        <v>0</v>
+      </c>
+      <c r="R178" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B179" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C179" s="1">
+        <v>2</v>
+      </c>
+      <c r="D179" s="1">
+        <v>9</v>
+      </c>
+      <c r="E179" s="1">
+        <v>0</v>
+      </c>
+      <c r="F179" s="1">
+        <v>0</v>
+      </c>
+      <c r="G179" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H179" s="1">
+        <v>1</v>
+      </c>
+      <c r="I179" s="1">
+        <v>0</v>
+      </c>
+      <c r="J179" s="1">
+        <v>0</v>
+      </c>
+      <c r="K179" s="1">
+        <v>0</v>
+      </c>
+      <c r="L179" s="1">
+        <v>0</v>
+      </c>
+      <c r="M179" s="1">
+        <v>0</v>
+      </c>
+      <c r="N179" s="1">
+        <v>0</v>
+      </c>
+      <c r="O179" s="1">
+        <v>0</v>
+      </c>
+      <c r="P179" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="1">
+        <v>0</v>
+      </c>
+      <c r="R179" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B180" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C180" s="1">
+        <v>2</v>
+      </c>
+      <c r="D180" s="1">
+        <v>8</v>
+      </c>
+      <c r="E180" s="1">
+        <v>0</v>
+      </c>
+      <c r="F180" s="1">
+        <v>0</v>
+      </c>
+      <c r="G180" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H180" s="1">
+        <v>2</v>
+      </c>
+      <c r="I180" s="1">
+        <v>0</v>
+      </c>
+      <c r="J180" s="1">
+        <v>0</v>
+      </c>
+      <c r="K180" s="1">
+        <v>0</v>
+      </c>
+      <c r="L180" s="1">
+        <v>0</v>
+      </c>
+      <c r="M180" s="1">
+        <v>0</v>
+      </c>
+      <c r="N180" s="1">
+        <v>0</v>
+      </c>
+      <c r="O180" s="1">
+        <v>0</v>
+      </c>
+      <c r="P180" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="1">
+        <v>0</v>
+      </c>
+      <c r="R180" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B181" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C181" s="1">
+        <v>2</v>
+      </c>
+      <c r="D181" s="1">
+        <v>8</v>
+      </c>
+      <c r="E181" s="1">
+        <v>1</v>
+      </c>
+      <c r="F181" s="1">
+        <v>0</v>
+      </c>
+      <c r="G181" s="1">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H181" s="1">
+        <v>0</v>
+      </c>
+      <c r="I181" s="1">
+        <v>0</v>
+      </c>
+      <c r="J181" s="1">
+        <v>0</v>
+      </c>
+      <c r="K181" s="1">
+        <v>0</v>
+      </c>
+      <c r="L181" s="1">
+        <v>0</v>
+      </c>
+      <c r="M181" s="1">
+        <v>0</v>
+      </c>
+      <c r="N181" s="1">
+        <v>0</v>
+      </c>
+      <c r="O181" s="1">
+        <v>0</v>
+      </c>
+      <c r="P181" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="1">
+        <v>0</v>
+      </c>
+      <c r="R181" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B182" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C182" s="1">
+        <v>2</v>
+      </c>
+      <c r="D182" s="1">
+        <v>7</v>
+      </c>
+      <c r="E182" s="1">
+        <v>0</v>
+      </c>
+      <c r="F182" s="1">
+        <v>0</v>
+      </c>
+      <c r="G182" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H182" s="1">
+        <v>0</v>
+      </c>
+      <c r="I182" s="1">
+        <v>0</v>
+      </c>
+      <c r="J182" s="1">
+        <v>9</v>
+      </c>
+      <c r="K182" s="1">
+        <v>0</v>
+      </c>
+      <c r="L182" s="1">
+        <v>0</v>
+      </c>
+      <c r="M182" s="1">
+        <v>0</v>
+      </c>
+      <c r="N182" s="1">
+        <v>0</v>
+      </c>
+      <c r="O182" s="1">
+        <v>0</v>
+      </c>
+      <c r="P182" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q182" s="1">
+        <v>0</v>
+      </c>
+      <c r="R182" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B183" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C183" s="1">
+        <v>2</v>
+      </c>
+      <c r="D183" s="1">
+        <v>7</v>
+      </c>
+      <c r="E183" s="1">
+        <v>2</v>
+      </c>
+      <c r="F183" s="1">
+        <v>0</v>
+      </c>
+      <c r="G183" s="1">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="H183" s="1">
+        <v>0</v>
+      </c>
+      <c r="I183" s="1">
+        <v>0</v>
+      </c>
+      <c r="J183" s="1">
+        <v>0</v>
+      </c>
+      <c r="K183" s="1">
+        <v>0</v>
+      </c>
+      <c r="L183" s="1">
+        <v>0</v>
+      </c>
+      <c r="M183" s="1">
+        <v>0</v>
+      </c>
+      <c r="N183" s="1">
+        <v>0</v>
+      </c>
+      <c r="O183" s="1">
+        <v>0</v>
+      </c>
+      <c r="P183" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q183" s="1">
+        <v>0</v>
+      </c>
+      <c r="R183" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B184" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C184" s="1">
+        <v>2</v>
+      </c>
+      <c r="D184" s="1">
+        <v>7</v>
+      </c>
+      <c r="E184" s="1">
+        <v>0</v>
+      </c>
+      <c r="F184" s="1">
+        <v>2</v>
+      </c>
+      <c r="G184" s="1">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="H184" s="1">
+        <v>0</v>
+      </c>
+      <c r="I184" s="1">
+        <v>0</v>
+      </c>
+      <c r="J184" s="1">
+        <v>0</v>
+      </c>
+      <c r="K184" s="1">
+        <v>0</v>
+      </c>
+      <c r="L184" s="1">
+        <v>0</v>
+      </c>
+      <c r="M184" s="1">
+        <v>0</v>
+      </c>
+      <c r="N184" s="1">
+        <v>0</v>
+      </c>
+      <c r="O184" s="1">
+        <v>0</v>
+      </c>
+      <c r="P184" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q184" s="1">
+        <v>0</v>
+      </c>
+      <c r="R184" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B185" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C185" s="1">
+        <v>2</v>
+      </c>
+      <c r="D185" s="1">
+        <v>7</v>
+      </c>
+      <c r="E185" s="1">
+        <v>0</v>
+      </c>
+      <c r="F185" s="1">
+        <v>2</v>
+      </c>
+      <c r="G185" s="1">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="H185" s="1">
+        <v>0</v>
+      </c>
+      <c r="I185" s="1">
+        <v>0</v>
+      </c>
+      <c r="J185" s="1">
+        <v>0</v>
+      </c>
+      <c r="K185" s="1">
+        <v>0</v>
+      </c>
+      <c r="L185" s="1">
+        <v>0</v>
+      </c>
+      <c r="M185" s="1">
+        <v>0</v>
+      </c>
+      <c r="N185" s="1">
+        <v>0</v>
+      </c>
+      <c r="O185" s="1">
+        <v>0</v>
+      </c>
+      <c r="P185" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q185" s="1">
+        <v>0</v>
+      </c>
+      <c r="R185" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B186" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C186" s="1">
+        <v>2</v>
+      </c>
+      <c r="D186" s="1">
+        <v>6</v>
+      </c>
+      <c r="E186" s="1">
+        <v>1</v>
+      </c>
+      <c r="F186" s="1">
+        <v>9</v>
+      </c>
+      <c r="G186" s="1">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="H186" s="1">
+        <v>0</v>
+      </c>
+      <c r="I186" s="1">
+        <v>0</v>
+      </c>
+      <c r="J186" s="1">
+        <v>0</v>
+      </c>
+      <c r="K186" s="1">
+        <v>0</v>
+      </c>
+      <c r="L186" s="1">
+        <v>0</v>
+      </c>
+      <c r="M186" s="1">
+        <v>0</v>
+      </c>
+      <c r="N186" s="1">
+        <v>0</v>
+      </c>
+      <c r="O186" s="1">
+        <v>0</v>
+      </c>
+      <c r="P186" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q186" s="1">
+        <v>0</v>
+      </c>
+      <c r="R186" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/Truth.xlsx
+++ b/data/Truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\AI Projects\otter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF0F2F9-8BFF-48A6-9257-612E5E2A238A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13000B91-A48C-46B0-ACD9-DD3CDFD845A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33435" yWindow="0" windowWidth="18525" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-45" yWindow="5565" windowWidth="19320" windowHeight="9690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8984,7 +8984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>163</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>162</v>
       </c>
@@ -9098,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>164</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>165</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>166</v>
       </c>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>167</v>
       </c>
@@ -9326,7 +9326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>168</v>
       </c>
@@ -9383,7 +9383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>169</v>
       </c>
@@ -9440,7 +9440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>170</v>
       </c>
@@ -9497,7 +9497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>171</v>
       </c>
@@ -9554,7 +9554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>172</v>
       </c>
@@ -9611,7 +9611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>173</v>
       </c>
@@ -9668,7 +9668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>174</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>175</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="G172" s="1">
-        <f t="shared" ref="G172:G188" si="8">SUM(E172:F172)</f>
+        <f t="shared" ref="G172:G186" si="8">SUM(E172:F172)</f>
         <v>0</v>
       </c>
       <c r="H172" s="1">
